--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -5452,7 +5452,7 @@
           <t>10 | 2955呎 (4+房)
 $38077万
 $128,857/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -5560,7 +5560,7 @@
           <t>10 | 2097呎 (3房)
 $16578万
 $79,056/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -5568,7 +5568,7 @@
           <t>11 | 2133呎 (4+房)
 $15570万
 $72,997/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
           <t>10 | 2153呎 (4+房)
 $14339万
 $66,600/呎
-(26年-07月-22日)</t>
+(26年-07月-23日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -5947,7 +5947,7 @@
           <t>8 | 2849呎 (4+房)
 $36200万
 $127,062/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6040,7 +6040,7 @@
           <t>9 | 2137呎 (4+房)
 $15707万
 $73,500/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6063,7 @@
           <t>9 | 2137呎 (4+房)
 $14959万
 $70,000/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
           <t>8 | 1875呎 (3房)
 $12656万
 $67,500/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">

--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -4035,7 +4035,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -6101,7 +6101,7 @@
           <t>8 | 1875呎 (3房)
 $12656万
 $67,500/呎
-(26年-07月-16日)</t>
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">

--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6081,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2137</v>
+        <v>2082</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3553,14 +3553,14 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
         <v>157069500</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>73500</v>
+        <v>75442</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3820,23 +3820,19 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>148751600</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>69608</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3845,12 +3841,12 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -3860,7 +3856,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3960,23 +3956,19 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>142110500</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>66500</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3985,12 +3977,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -4000,7 +3992,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4088,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -4106,12 +4098,12 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -4121,12 +4113,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -4136,7 +4128,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5895,27 +5887,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -6037,10 +6029,10 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>9 | 2137呎 (4+房)
+          <t>9 | 2082呎 (4+房)
 $15707万
-$73,500/呎
-(26年-07月-09日)</t>
+$75,442/呎
+(26年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6073,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
+$14875万
+$69,608/呎
+(26年-08月-04日)</t>
         </is>
       </c>
     </row>
@@ -6104,35 +6096,35 @@
 (26年-07月-31日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>9 | 2137呎 (4+房)
+$14211万
+$66,500/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>8 | 1875呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
 招标单位
 -
 (在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>8 | 1875呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>9 | 2137呎 (4+房)
--
--
-(待售)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -4088,23 +4088,19 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>140614600</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>65800</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4113,12 +4109,12 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -4128,7 +4124,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5883,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5897,7 +5893,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -6119,12 +6115,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
-招标单位
--
-(在售)</t>
+$14061万
+$65,800/呎
+(26年-08月-10日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -1741,7 +1741,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -5594,7 +5594,7 @@
           <t>10 | 2153呎 (4+房)
 $14339万
 $66,600/呎
-(26年-07月-23日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">

--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -4093,7 +4093,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -6120,7 +6120,7 @@
           <t>9 | 2137呎 (4+房)
 $14061万
 $65,800/呎
-(26年-08月-10日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -1324,23 +1324,19 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>159322000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>74000</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1349,12 +1345,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1364,7 +1360,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5384,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5398,7 +5394,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -5520,12 +5516,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>10 | 2153呎 (4+房)
-招标单位
--
-(在售)</t>
+$15932万
+$74,000/呎
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">

--- a/web/files/港岛-半山区西部-应天.xlsx
+++ b/web/files/港岛-半山区西部-应天.xlsx
@@ -3957,7 +3957,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6093,7 @@
           <t>9 | 2137呎 (4+房)
 $14211万
 $66,500/呎
-(26年-08月-04日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -6157,12 +6157,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>9 | 2137呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
